--- a/data/Table 1. Source overview.xlsx
+++ b/data/Table 1. Source overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\02学习\2025summer\JDH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\02学习\2025summer\JDH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322ACBD8-C772-4C87-AF37-E730FA3B77BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A692F9-A455-4F6F-8ED0-135C2024C630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="2910" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Source</t>
   </si>
@@ -69,18 +69,6 @@
     <t>address strings; no native coords</t>
   </si>
   <si>
-    <t>Mattson (2019; 2021)</t>
-  </si>
-  <si>
-    <t>national interpretive frame</t>
-  </si>
-  <si>
-    <t>national scale context (not row-ingested)</t>
-  </si>
-  <si>
-    <t>critique of market-facing categories</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
@@ -96,21 +84,6 @@
     <t>authoritative admin/cartographic</t>
   </si>
   <si>
-    <t>Participant sessions (transcripts + sketch maps)</t>
-  </si>
-  <si>
-    <t>project-produced primary corpus</t>
-  </si>
-  <si>
-    <t>sessions (10)</t>
-  </si>
-  <si>
-    <t>analytic codebook</t>
-  </si>
-  <si>
-    <t>non-metric sketches + toponyms</t>
-  </si>
-  <si>
     <t>Required derivations</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -131,27 +104,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>category drift in commercial listings</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>administrative boundary effects</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>—</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>coding; overlapping sketches</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>present-tense session time; narrated time in interview (2013-2025)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>situated, present-tense accounts; recall and abstraction; non-representativeness</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -559,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.9140625" customWidth="1"/>
@@ -584,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -593,10 +550,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -605,16 +562,16 @@
     </row>
     <row r="2" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -623,10 +580,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="2"/>
@@ -635,28 +592,28 @@
     </row>
     <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="2"/>
@@ -683,28 +640,28 @@
         <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
@@ -713,67 +670,21 @@
         <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="2"/>
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
